--- a/subsystems database (archivedcopy).xlsx
+++ b/subsystems database (archivedcopy).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conal\Desktop\PhD\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAFE0D43-40A4-45AE-8F08-056EEDFB3BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBB0862-828A-4A8E-A3F8-F591E1309714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-795" windowWidth="29040" windowHeight="15720" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -228,7 +228,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -545,14 +545,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EAA883-65ED-4288-9D11-90A18C3BBAF4}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -593,7 +593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -632,7 +632,7 @@
       </c>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -671,7 +671,7 @@
       </c>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -710,7 +710,7 @@
       </c>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -749,7 +749,7 @@
       </c>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -829,7 +829,7 @@
       </c>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -868,7 +868,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -905,7 +905,7 @@
       </c>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -946,7 +946,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -987,7 +987,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>

--- a/subsystems database (archivedcopy).xlsx
+++ b/subsystems database (archivedcopy).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conal\Desktop\PhD\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBB0862-828A-4A8E-A3F8-F591E1309714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BE0AB5-A101-4EAD-84FD-BE99C5300828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
   </bookViews>
